--- a/artfynd/A 26857-2021 artfynd.xlsx
+++ b/artfynd/A 26857-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128323606</v>
       </c>
       <c r="B2" t="n">
-        <v>107358</v>
+        <v>107363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128326421</v>
       </c>
       <c r="B3" t="n">
-        <v>107358</v>
+        <v>107363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128322689</v>
       </c>
       <c r="B4" t="n">
-        <v>103930</v>
+        <v>103935</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26857-2021 artfynd.xlsx
+++ b/artfynd/A 26857-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128323606</v>
       </c>
       <c r="B2" t="n">
-        <v>107363</v>
+        <v>107456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128326421</v>
       </c>
       <c r="B3" t="n">
-        <v>107363</v>
+        <v>107456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128322689</v>
       </c>
       <c r="B4" t="n">
-        <v>103935</v>
+        <v>104028</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26857-2021 artfynd.xlsx
+++ b/artfynd/A 26857-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128323606</v>
       </c>
       <c r="B2" t="n">
-        <v>107456</v>
+        <v>107479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128326421</v>
       </c>
       <c r="B3" t="n">
-        <v>107456</v>
+        <v>107479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128322689</v>
       </c>
       <c r="B4" t="n">
-        <v>104028</v>
+        <v>104049</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26857-2021 artfynd.xlsx
+++ b/artfynd/A 26857-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128323606</v>
       </c>
       <c r="B2" t="n">
-        <v>107479</v>
+        <v>107491</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128326421</v>
       </c>
       <c r="B3" t="n">
-        <v>107479</v>
+        <v>107491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128322689</v>
       </c>
       <c r="B4" t="n">
-        <v>104049</v>
+        <v>104061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26857-2021 artfynd.xlsx
+++ b/artfynd/A 26857-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128323606</v>
       </c>
       <c r="B2" t="n">
-        <v>107491</v>
+        <v>107500</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128326421</v>
       </c>
       <c r="B3" t="n">
-        <v>107491</v>
+        <v>107500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128322689</v>
       </c>
       <c r="B4" t="n">
-        <v>104061</v>
+        <v>104070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26857-2021 artfynd.xlsx
+++ b/artfynd/A 26857-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128323606</v>
       </c>
       <c r="B2" t="n">
-        <v>107500</v>
+        <v>107505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128326421</v>
       </c>
       <c r="B3" t="n">
-        <v>107500</v>
+        <v>107505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128322689</v>
       </c>
       <c r="B4" t="n">
-        <v>104070</v>
+        <v>104073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26857-2021 artfynd.xlsx
+++ b/artfynd/A 26857-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128323606</v>
       </c>
       <c r="B2" t="n">
-        <v>107505</v>
+        <v>107533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128326421</v>
       </c>
       <c r="B3" t="n">
-        <v>107505</v>
+        <v>107533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128322689</v>
       </c>
       <c r="B4" t="n">
-        <v>104073</v>
+        <v>104100</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26857-2021 artfynd.xlsx
+++ b/artfynd/A 26857-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128323606</v>
       </c>
       <c r="B2" t="n">
-        <v>107533</v>
+        <v>107546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128326421</v>
       </c>
       <c r="B3" t="n">
-        <v>107533</v>
+        <v>107546</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128322689</v>
       </c>
       <c r="B4" t="n">
-        <v>104100</v>
+        <v>104113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 26857-2021 artfynd.xlsx
+++ b/artfynd/A 26857-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128323606</v>
       </c>
       <c r="B2" t="n">
-        <v>107546</v>
+        <v>107550</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>128326421</v>
       </c>
       <c r="B3" t="n">
-        <v>107546</v>
+        <v>107550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>128322689</v>
       </c>
       <c r="B4" t="n">
-        <v>104113</v>
+        <v>104117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
